--- a/Documentation/Best For Weighting Tables/Best for Seniors Living Alone.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Seniors Living Alone.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C18831D-13B2-48DD-BFE5-4B40D86C5741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B63F01-B790-4967-8F50-F9FCFC656DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{E25008BD-21E9-4A74-A844-E55480A146D5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E25008BD-21E9-4A74-A844-E55480A146D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Seniors Living Alone" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Feature</t>
   </si>
@@ -69,15 +69,6 @@
   </si>
   <si>
     <t>Value for money</t>
-  </si>
-  <si>
-    <t>Sound</t>
-  </si>
-  <si>
-    <t>Realism</t>
-  </si>
-  <si>
-    <t>size and weight</t>
   </si>
 </sst>
 </file>
@@ -469,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA8E79C3-86E9-406F-804D-5C9D24E66759}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" style="2" customWidth="1"/>
@@ -549,30 +540,6 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
